--- a/data_extactor/batch_10_fa/batch_0086_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0086_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | مانیتورینگ | تفکر انتقادی | سخن گفتن</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دقت کنترل | چالاکی دست | بینایی نزدیک | حساسیت به مشکل | زمان عکس‌العمل | هماهنگی چند عضو | ثبات بازو-دست | سرعت ادراکی | کنترل نرخ | درک عمق | بینایی دور | قدرت تنه | قدرت ایستا | چالاکی انگشتان | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنیداری | سرعت مچ-انگشت</t>
+          <t>دقت کنترل | مهارت دستی | بینایی نزدیک | حساسیت به مسئله | زمان عکس‌العمل | هماهنگی چند عضو | ثبات دست و بازو | سرعت ادراکی | کنترل نرخ | درک عمق | بینایی دور | قدرت تنه | قدرت ایستا | مهارت انگشتان | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنیداری | سرعت مچ و انگشتان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا منظم بودن | فشار زمانی | داخل ساختمان، با تهویه مطبوع | صرف زمان به صورت ایستاده | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | سلامت و ایمنی سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | سرعت تعیین‌شده توسط سرعت تجهیزات | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردکن، سنگ‌زنی و پرداخت | برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مته‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | مانیتورینگ | گوش دادن فعال</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | مهندسی و فناوری | آموزش و پرورش | مدیریت و امور اداری | خدمات مشتریان و پرسنل | زبان انگلیسی | ریاضیات</t>
+          <t>تولید و فرآوری | مکانیک | مهندسی و فناوری | آموزش و پرورش | مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | دقت کنترل | بینایی نزدیک | چالاکی انگشتان | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | چالاکی دست | تجسم فضایی | حساسیت به مشکل | درک شفاهی | قدرت تنه | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت انگشتان | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | مهارت دستی | تجسم | حساسیت به مسئله | درک شفاهی | قدرت تنه | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | داخل ساختمان، با تهویه مطبوع | صرف زمان به صورت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران | اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مته‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترودینگ و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | EditCNC | زبان نشانه‌گذاری گسترش‌پذیر XML | G-code | نرم‌افزار کارگاهی Kentech | M-code | نرم‌افزار طراحی و تولید کامپیوتری Mastercam | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | SWIVEL Software | Siemens Solid Edge | SmartCAMcnc SmartCAM | Vero Software ALPHACAM | Vero Software Edgecam</t>
+          <t>Autodesk AutoCAD | EditCNC | زبان نشانه‌گذاری توسعه‌پذیر XML | G-code | نرم‌افزار کارگاهی Kentech | M-code | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | SWIVEL Software | Siemens Solid Edge | SmartCAMcnc SmartCAM | Vero Software ALPHACAM | Vero Software Edgecam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چالاکی دست | بینایی نزدیک | دقت کنترل | ثبات بازو-دست | حساسیت به مشکل | هماهنگی چند عضو | زمان عکس‌العمل | قدرت تنه | چالاکی انگشتان | توجه انتخابی | تجسم فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | استدلال استقرایی | بیان شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | هماهنگی چند عضو | زمان عکس‌العمل | قدرت تنه | مهارت انگشتان | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا منظم بودن | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، بدون تهویه مطبوع | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مته‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات کشش و اکستروژن فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورهای ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | ماشین‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار چاپ سه‌بعدی | نرم‌افزار Armchair Machinist | Autodesk AutoCAD | Autodesk Fusion 360 | Autodesk HSMWorks | ماشین‌حساب ماشین‌کاری CNC Consulting | CNC Mastercam | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ERP | EditCNC | G-code | GRZ Software MeshCAM | Hexagon Metrology PC-DMIS | IMSI TurboCAD | JETCAM | JobBOSS | Kentech Kipware Studio | Kentech Kipware Trig Kalculator | نرم‌افزار طراحی و تولید کامپیوتری Mastercam | Mazak Mazatrol SMART CNC | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OnShape | OneCNC CAD/CAM | PTC Creo Parametric | نرم‌افزار SAP | Siemens NX | نرم‌افزار SolidCAM CAM | Vero Software SURFCAM</t>
+          <t>نرم‌افزار چاپ سه‌بعدی | نرم‌افزار Armchair Machinist | Autodesk AutoCAD | Autodesk Fusion 360 | Autodesk HSMWorks | ماشین‌حساب ماشین‌کاری CNC Consulting | CNC Mastercam | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار ERP | EditCNC | G-code | GRZ Software MeshCAM | Hexagon Metrology PC-DMIS | IMSI TurboCAD | JETCAM | JobBOSS | Kentech Kipware Studio | Kentech Kipware Trig Kalculator | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Mazak Mazatrol SMART CNC | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | OnShape | OneCNC CAD/CAM | PTC Creo Parametric | نرم‌افزار SAP | Siemens NX | نرم‌افزار SolidCAM CAM | Vero Software SURFCAM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | سخن گفتن | گوش دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | چالاکی دست | چالاکی انگشتان | دقت کنترل | بینایی نزدیک | حساسیت به مشکل | استدلال قیاسی | توجه انتخابی | کنترل نرخ | هماهنگی چند عضو | تجسم فضایی | ترتیب‌دهی اطلاعات | درک شفاهی | انعطاف‌پذیری مقوله‌ها | استدلال استقرایی | بیان شفاهی | درک کتبی | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | کنترل نرخ | هماهنگی چند عضو | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا منظم بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | آزادی در تصمیم‌گیری | داخل ساختمان، با تهویه مطبوع | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | سلامت و ایمنی سایر کارگران | تعداد دفعات تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | فناوران و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات مته‌کاری و بورینگ فلز و پلاستیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | سازندگان و نصابان ماشین‌آلات صنعتی | مدل‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | سازندگان و جفت‌کنندگان فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سوراخ‌کاری و بورینگ، فلز و پلاستیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان نصب ماشین‌آلات | مدل‌سازان فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | امنیت و ایمنی عمومی | مدیریت و امور اداری | آموزش و پرورش</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | حساسیت به مشکل | چالاکی دست | بینایی نزدیک | زمان عکس‌العمل | ثبات بازو-دست | توجه انتخابی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | حساسیت شنیداری | درک عمق | انعطاف‌پذیری بدنی | قدرت ایستا | کنترل نرخ | سرعت ادراکی | استدلال قیاسی | جهت‌گیری پاسخ | چالاکی انگشتان | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | حساسیت به درخشندگی نور | تشخیص رنگ‌های بصری | قدرت تنه | توجه شنیداری</t>
+          <t>دقت کنترل | حساسیت به مسئله | مهارت دستی | بینایی نزدیک | زمان عکس‌العمل | ثبات دست و بازو | توجه انتخابی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | حساسیت شنوایی | درک عمق | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | کنترل نرخ | سرعت ادراکی | استدلال قیاسی | جهت‌گیری پاسخ | مهارت انگشتان | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | حساسیت به درخشندگی شدید | تشخیص رنگ بصری | قدرت تنه | توجه شنیداری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | سلامت و ایمنی سایر کارگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، بدون تهویه مطبوع | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | پیامدهای کاری و نتایج سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض شرایط خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترودینگ و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره، کوره پخت، آون، خشک‌کن و دیگ ذوب | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آبکاری فلز و پلاستیک | ریزندگان و ریخته‌گران فلز | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | تعمیرکاران مواد نسوز، به جز بناهای آجر نسوز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | جوشکاران، برش‌کاران و لحیم‌کاران | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای کمپرسور گاز و ایستگاه پمپاژ گاز | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | ریزندگان و ریخته‌گران فلز | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | دقت کنترل | چالاکی دست | بینایی نزدیک | زمان عکس‌العمل | هماهنگی چند عضو | سرعت ادراکی | قدرت تنه | چالاکی انگشتان | توجه انتخابی | انعطاف‌پذیری مقوله‌ها | حساسیت به مشکل | درک شفاهی</t>
+          <t>ثبات دست و بازو | دقت کنترل | مهارت دستی | بینایی نزدیک | زمان عکس‌العمل | هماهنگی چند عضو | سرعت ادراکی | قدرت تنه | مهارت انگشتان | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، بدون تهویه مطبوع | صرف زمان به صورت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا منظم بودن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات کشش و اکستروژن فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترودینگ و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات آبکاری فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجر نسوز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ</t>
+          <t>تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | تجسم فضایی | ثبات بازو-دست | چالاکی دست | چالاکی انگشتان | دقت کنترل | ترتیب‌دهی اطلاعات | درک کتبی | حساسیت به مشکل | درک شفاهی | زمان عکس‌العمل | استدلال قیاسی | توجه انتخابی | هماهنگی چند عضو | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری مقوله‌ها | استدلال استقرایی | نگارش کتبی | بیان شفاهی | توجه شنیداری | بینایی دور | قدرت تنه | قدرت ایستا</t>
+          <t>بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | ترتیب‌دهی اطلاعات | درک کتبی | حساسیت به مسئله | درک شفاهی | زمان عکس‌العمل | استدلال قیاسی | توجه انتخابی | هماهنگی چند عضو | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | توجه شنیداری | بینایی دور | قدرت تنه | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا منظم بودن | صرف زمان به صورت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | داخل ساختمان، با تهویه مطبوع | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | فناوران و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | پیاده‌سازان طرح فلز و پلاستیک | ماشین‌کاران | نقشه‌کشان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | الگوسازان فلز و پلاستیک | ورق‌کاران | سازندگان و جفت‌کنندگان فلزات سازه‌ای | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای ابزار کنترل عددی کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | نقشه‌کشان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | الگوسازان فلز و پلاستیک | کارگران ورق‌کاری | سازندگان و مونتاژکاران فلزات سازه‌ای | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار طراحی و تولید کامپیوتری Mastercam | Microsoft Excel | Microsoft Outlook</t>
+          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات بازو-دست | حساسیت به مشکل | تجسم فضایی | چالاکی دست | دقت کنترل | چالاکی انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری مقوله‌ها | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | تشخیص گفتار | وضوح گفتار</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | تجسم | مهارت دستی | دقت کنترل | مهارت انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | تشخیص گفتار | وضوح گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | صرف زمان به صورت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارگران | سلامت و ایمنی سایر کارگران | داخل ساختمان، با تهویه مطبوع</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض تجهیزات خطرناک | مکالمات تلفنی | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | نزدیکی فیزیکی | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | حکاکان و تیزکنندگان | الگوسازان پارچه و پوشاک | کارگران سنگ‌زنی و پرداخت دستی | پیاده‌سازان طرح فلز و پلاستیک | ماشین‌کاران | نقشه‌کشان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | ورق‌کاران | سازندگان و جفت‌کنندگان فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | حکاکان و تیزاب‌کاران | الگوسازان پارچه و پوشاک | کارگران سنگ‌زنی و پرداخت دستی | کارگران شابلون‌زنی، فلز و پلاستیک | ماشین‌کاران | نقشه‌کشان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | کارگران ورق‌کاری | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ</t>
+          <t>نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مکانیک | آموزش و پرورش | تولید و فرآوری | مدیریت و امور اداری | فیزیک | طراحی | مهندسی و فناوری</t>
+          <t>زبان انگلیسی | مکانیک | آموزش و پرورش | تولید و فرآوری | مدیریت و اداره | فیزیک | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>قدرت تنه | چالاکی دست | قدرت ایستا | ثبات بازو-دست | چالاکی انگشتان | هماهنگی چند عضو | بینایی نزدیک | زمان عکس‌العمل | حساسیت به مشکل | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم فضایی | ترتیب‌دهی اطلاعات | درک شفاهی</t>
+          <t>قدرت تنه | مهارت دستی | قدرت ایستا | ثبات دست و بازو | مهارت انگشتان | هماهنگی چند عضو | بینایی نزدیک | زمان عکس‌العمل | حساسیت به مسئله | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، بدون تهویه مطبوع | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا منظم بودن | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سرعت تعیین‌شده توسط سرعت تجهیزات | تعداد دفعات تصمیم‌گیری | سلامت و ایمنی سایر کارگران</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض تجهیزات خطرناک | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سرعت تعیین‌شده توسط سرعت تجهیزات | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌کاران و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترودینگ و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | لایه‌نشانان و سازندگان فایبرگلاس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | الگوسازان فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجر نسوز | اپراتورها و متصدیان ماشین‌آلات کفش‌دوزی | سازندگان و جفت‌کنندگان فلزات سازه‌ای | کارگران و پرداخت‌کاران موزاییک سیمانی | سازندگان تایر | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | لمینت‌کاران و سازندگان فایبرگلاس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | الگوسازان فلز و پلاستیک | تعمیرکاران مواد نسوز، به جز بناهای آجرکار | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | سازندگان و مونتاژکاران فلزات سازه‌ای | کارگران و پرداخت‌کاران ترازو | تایر سازان | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | مانیتورینگ | درک مطلب | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | چالاکی دست | هماهنگی چند عضو | دقت کنترل | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی نزدیک | وضوح گفتار | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | کنترل نرخ | چالاکی انگشتان | انعطاف‌پذیری مقوله‌ها | حساسیت به مشکل | بیان شفاهی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | تشخیص گفتار | توجه شنیداری | توجه انتخابی | تجسم فضایی</t>
+          <t>ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | دقت کنترل | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی نزدیک | وضوح گفتار | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | کنترل نرخ | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | تشخیص گفتار | توجه شنیداری | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | اهمیت دقیق یا منظم بودن | فشار زمانی | آزادی در تصمیم‌گیری | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گازگرفتگی‌ها یا نیش‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارگران | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | فشار زمانی | آزادی در تصمیم‌گیری | ارتباط با دیگران | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌آلات اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات کشش و اکستروژن فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکسترودینگ و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فورجینگ فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نورد فلز و پلاستیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جوشکاری، لحیم‌کاری نرم و سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0086_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0086_fa.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فراوری</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>کنترل دقیق | چابکی دستی | دید نزدیک | حساسیت به مسئله | زمان واکنش | هماهنگی چندعضوی | پایداری دست و بازو | سرعت ادراک | کنترل نرخ | درک عمق | دید دور | استحکام بالاتنه | قدرت ایستا | چابکی انگشتان | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنیداری | سرعت مچ و انگشتان</t>
+          <t>دقت کنترل | مهارت دستی | بینایی نزدیک | حساسیت به مسئله | زمان عکس‌العمل | هماهنگی چند عضو | ثبات دست و بازو | سرعت ادراکی | کنترل نرخ | درک عمق | بینایی دور | قدرت تنه | قدرت ایستا | مهارت انگشتان | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی | استدلال استقرایی | بیان شفاهی | درک شفاهی | توجه شنیداری | سرعت مچ و انگشتان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای دستگاه‌های خردایش، سنگ‌زنی و پرداخت | برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | تعمیرکاران ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌آلات محصولات کاغذی | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای اره‌کاری چوب | تنظیم‌کاران و اپراتورهای ماشین‌های برش پارچه و منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | مهندسی و فناوری | آموزش و تدریس | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات</t>
+          <t>تولید و فرآوری | مکانیک | مهندسی و فناوری | آموزش و پرورش | مدیریت و اداره | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | کنترل دقیق | دید نزدیک | چابکی انگشتان | زمان واکنش | کنترل نرخ | هماهنگی چندعضوی | چابکی دستی | تجسم فضایی | حساسیت به مسئله | درک شفاهی | استحکام بالاتنه | توجه انتخابی | سرعت ادراک | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت انگشتان | زمان عکس‌العمل | کنترل نرخ | هماهنگی چند عضو | مهارت دستی | تجسم | حساسیت به مسئله | درک شفاهی | قدرت تنه | توجه انتخابی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان شفاهی | درک کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سیم‌پیچ‌ها و پرداخت‌کاران | اپراتورهای ابزارهای CNC | تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف شیشه و سنتزی | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | تراشکاران و ماشین‌کاران | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های برش پارچه و منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | زبان انگلیسی | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | کنترل دقیق | پایداری دست و بازو | حساسیت به مسئله | هماهنگی چندعضوی | زمان واکنش | استحکام بالاتنه | چابکی انگشتان | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | استدلال استقرایی | بیان شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | هماهنگی چند عضو | زمان عکس‌العمل | قدرت تنه | مهارت انگشتان | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک شفاهی | درک کتبی | تشخیص گفتار | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزارهای CNC | تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | تراشکاران و ماشین‌کاران | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای اره‌کاری چوب | تنظیم‌کاران و اپراتورهای ماشین‌های برش پارچه و منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | مکانیک | تولید و فراوری | طراحی</t>
+          <t>ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | چابکی انگشتان | کنترل دقیق | دید نزدیک | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | کنترل نرخ | هماهنگی چندعضوی | تجسم فضایی | مرتب‌سازی اطلاعات | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | زمان واکنش | سرعت ادراک | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | کنترل نرخ | هماهنگی چند عضو | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | زمان عکس‌العمل | سرعت ادراکی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | اپراتورهای ابزارهای CNC | برنامه‌نویسان ماشین‌های کنترل عددی رایانه‌ای CNC | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | مونتاژکاران تجهیزات برقی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک‌های نصب ماشین‌آلات صنعتی و پایش خطوط (میلرایت) | مدل‌سازان فلز و پلاستیک | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | سازندگان و فیت‌کارهای سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مدل‌سازان فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>کنترل دقیق | حساسیت به مسئله | چابکی دستی | دید نزدیک | زمان واکنش | پایداری دست و بازو | توجه انتخابی | مرتب‌سازی اطلاعات | هماهنگی چندعضوی | حساسیت شنوایی | درک عمق | انعطاف‌پذیری دامنه‌ای | قدرت ایستا | کنترل نرخ | سرعت ادراک | استدلال قیاسی | جهت‌یابی پاسخ | چابکی انگشتان | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | حساسیت به درخشش | تمایز رنگ‌های بینایی | استحکام بالاتنه | توجه شنیداری</t>
+          <t>دقت کنترل | حساسیت به مسئله | مهارت دستی | بینایی نزدیک | زمان عکس‌العمل | ثبات دست و بازو | توجه انتخابی | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | حساسیت شنوایی | درک عمق | انعطاف‌پذیری دامنه حرکت | قدرت ایستا | کنترل نرخ | سرعت ادراکی | استدلال قیاسی | جهت‌گیری پاسخ | مهارت انگشتان | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | حساسیت به درخشندگی شدید | تشخیص رنگ بصری | قدرت تنه | توجه شنیداری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، چربی‌زدایی و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات برودتی و انجماد | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف شیشه و سنتزی | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و اتوکلاوها | اپراتورهای کمپرسور گاز و ایستگاه‌های پمپاژ گاز | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های آبکاری و پوشش‌دهی فلز و پلاستیک | ریخته‌گران و متصدیان بارریزی مذاب فلزات | اپراتورهای پمپ به‌جز پمپ‌های سرچاهی | تعمیرکاران و نسوزکاران مواد دیرگداز به‌جز بناها | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های جداسازی، فیلتراسیون، زلال‌سازی، رسوب‌گیری و تقطیر | مهندسان تاسیسات و اپراتورهای دیگ بخار (بویلر) | جوشکاران، برشکاران و لحیم‌کاران | تنظیم‌کاران و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>تکنسین‌های نیروگاه زیست‌توده | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | ریخته‌گران و متصدیان بارریزی مذاب فلزات | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | کنترل دقیق | چابکی دستی | دید نزدیک | زمان واکنش | هماهنگی چندعضوی | سرعت ادراک | استحکام بالاتنه | چابکی انگشتان | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک شفاهی</t>
+          <t>ثبات دست و بازو | دقت کنترل | مهارت دستی | بینایی نزدیک | زمان عکس‌العمل | هماهنگی چند عضو | سرعت ادراکی | قدرت تنه | مهارت انگشتان | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | درک شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف شیشه و سنتزی | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | تعمیرکاران ماشین‌آلات صنعتی | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های آبکاری و پوشش‌دهی فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز به‌جز بناها | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های جداسازی، فیلتراسیون، زلال‌سازی، رسوب‌گیری و تقطیر | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | تولید و فراوری | طراحی | مهندسی و فناوری</t>
+          <t>مکانیک | ریاضیات | تولید و فرآوری | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم فضایی | پایداری دست و بازو | چابکی دستی | چابکی انگشتان | کنترل دقیق | مرتب‌سازی اطلاعات | درک کتبی | حساسیت به مسئله | درک شفاهی | زمان واکنش | استدلال قیاسی | توجه انتخابی | هماهنگی چندعضوی | کنترل نرخ | سرعت ادراک | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | توجه شنیداری | دید دور | استحکام بالاتنه | قدرت ایستا</t>
+          <t>بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | ترتیب‌دهی اطلاعات | درک کتبی | حساسیت به مسئله | درک شفاهی | زمان عکس‌العمل | استدلال قیاسی | توجه انتخابی | هماهنگی چند عضو | کنترل نرخ | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | بیان شفاهی | توجه شنیداری | بینایی دور | قدرت تنه | قدرت ایستا</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | اپراتورهای ابزارهای CNC | برنامه‌نویسان ماشین‌های کنترل عددی رایانه‌ای CNC | مونتاژکاران تجهیزات برقی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و ماشین‌آلات صنعتی | مکانیک‌های ماشین‌آلات صنعتی | خط‌کش‌ها و نشانه‌گذاران فلز و پلاستیک | تراشکاران و ماشین‌کاران | نقشه‌کش‌های مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | الگو سازان فلز و پلاستیک | سازندگان سازه‌های ورق‌کاری و کانال‌سازان فلزی | سازندگان و فیت‌کارهای سازه‌های فلزی | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | الگوسازان فلز و پلاستیک | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار CAD/CAM طراحی و ساخت Mastercam | Microsoft Excel | Microsoft Outlook</t>
+          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | ریاضیات | طراحی | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | حساسیت به مسئله | تجسم فضایی | چابکی دستی | کنترل دقیق | چابکی انگشتان | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | تشخیص گفتار | وضوح گفتار</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | تجسم | مهارت دستی | دقت کنترل | مهارت انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان شفاهی | درک کتبی | درک شفاهی | تشخیص گفتار | وضوح گفتار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | قلم‌زنان و حکاکان | الگوسازان پارچه و پوشاک | کارگران سنگ‌زنی و پرداخت دستی | خط‌کش‌ها و نشانه‌گذاران فلز و پلاستیک | تراشکاران و ماشین‌کاران | نقشه‌کش‌های مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | سازندگان سازه‌های ورق‌کاری و کانال‌سازان فلزی | سازندگان و فیت‌کارهای سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | حکاکان و اسیدکاران | الگوسازان پارچه و پوشاک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | مدل‌سازان چوب | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | کارگران ورق‌کاری فلزی | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مکانیک | آموزش و تدریس | تولید و فراوری | مدیریت و امور اداری | فیزیک | طراحی | مهندسی و فناوری</t>
+          <t>زبان انگلیسی | مکانیک | آموزش و پرورش | تولید و فرآوری | مدیریت و اداره | فیزیک | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استحکام بالاتنه | چابکی دستی | قدرت ایستا | پایداری دست و بازو | چابکی انگشتان | هماهنگی چندعضوی | دید نزدیک | زمان واکنش | حساسیت به مسئله | توجه شنیداری | کنترل دقیق | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>قدرت تنه | مهارت دستی | قدرت ایستا | ثبات دست و بازو | مهارت انگشتان | هماهنگی چند عضو | بینایی نزدیک | زمان عکس‌العمل | حساسیت به مسئله | توجه شنیداری | دقت کنترل | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>برش‌کاران و پیراسته‌کاران دستی | تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف شیشه و سنتزی | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | سازندگان و لمینت‌کاران فایبرگلاس | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | الگو سازان فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز به‌جز بناها | اپراتورها و متصدیان ماشین‌آلات کفاشی | سازندگان و فیت‌کارهای سازه‌های فلزی | کارگران و پرداخت‌کاران سنگ موزاییک و ترازو | سازندگان تایر | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | لایه‌نشانان و سازندگان فایبرگلاس | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | الگوسازان فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | سازندگان و مونتاژکاران سازه‌های فلزی | موزاییک‌کاران و پرداخت‌کاران terrazzo | سازندگان تایر | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | درک مطلب | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | ریاضیات</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | هماهنگی چندعضوی | کنترل دقیق | استدلال قیاسی | مرتب‌سازی اطلاعات | سرعت ادراک | دید نزدیک | وضوح گفتار | استحکام بالاتنه | قدرت ایستا | زمان واکنش | کنترل نرخ | چابکی انگشتان | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | تشخیص گفتار | توجه شنیداری | توجه انتخابی | تجسم فضایی</t>
+          <t>ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | دقت کنترل | استدلال قیاسی | ترتیب‌دهی اطلاعات | سرعت ادراکی | بینایی نزدیک | وضوح گفتار | قدرت تنه | قدرت ایستا | زمان عکس‌العمل | کنترل نرخ | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | بیان شفاهی | درک کتبی | درک شفاهی | انعطاف‌پذیری بستار | استدلال استقرایی | تشخیص گفتار | توجه شنیداری | توجه انتخابی | تجسم</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران و اپراتورهای ماشین‌های برش و اسلایس | تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و فرم‌دهی الیاف شیشه و سنتزی | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن، فرم‌دهی، پرس و فشرده‌سازی | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | تنظیم‌کاران و اپراتورهای چندکاره ماشین‌ابزار فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان | تنظیم‌کاران و اپراتورهای ماشین‌های جوشکاری و لحیم‌کاری | تنظیم‌کاران و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
